--- a/inputData/inputDataMini.xlsx
+++ b/inputData/inputDataMini.xlsx
@@ -8,15 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sillewiberg/Desktop/Skole/Speciale/Master-Thesis-eVTOL-1/inputData/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{643F0648-698E-684C-B0F1-CDBD89F8120B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9FAAB28-105B-574D-B4E1-4D70D006A8C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16340" activeTab="2" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
+    <workbookView xWindow="11940" yWindow="500" windowWidth="16860" windowHeight="16340" activeTab="2" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>
   <sheets>
     <sheet name="PlaneData" sheetId="8" r:id="rId1"/>
     <sheet name="Infrastructure" sheetId="6" r:id="rId2"/>
     <sheet name="PassengerGroups" sheetId="5" r:id="rId3"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId4"/>
+  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -38,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="25">
   <si>
     <t>type</t>
   </si>
@@ -106,10 +109,13 @@
     <t>Base Vertiport</t>
   </si>
   <si>
-    <t>time_old</t>
-  </si>
-  <si>
     <t>coordinates</t>
+  </si>
+  <si>
+    <t>unit time</t>
+  </si>
+  <si>
+    <t>minuts/unit</t>
   </si>
 </sst>
 </file>
@@ -157,10 +163,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -176,6 +184,30 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Parameters"/>
+      <sheetName val="Prices"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="20">
+          <cell r="B20">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -558,7 +590,7 @@
         <v>3</v>
       </c>
       <c r="D1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
@@ -654,13 +686,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E3CF6DF-5DC6-4F82-AD2C-07BC625FD2D9}">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="5" max="5" width="19.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>14</v>
       </c>
@@ -671,7 +703,7 @@
         <v>16</v>
       </c>
       <c r="D1" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E1" t="s">
         <v>18</v>
@@ -679,11 +711,8 @@
       <c r="F1" t="s">
         <v>19</v>
       </c>
-      <c r="G1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -694,6 +723,7 @@
         <v>3</v>
       </c>
       <c r="D2">
+        <f>25/B11</f>
         <v>25</v>
       </c>
       <c r="E2">
@@ -702,12 +732,8 @@
       <c r="F2">
         <v>1</v>
       </c>
-      <c r="G2">
-        <f>D2/5</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -718,6 +744,7 @@
         <v>1</v>
       </c>
       <c r="D3">
+        <f>50/B11</f>
         <v>50</v>
       </c>
       <c r="E3">
@@ -726,12 +753,8 @@
       <c r="F3">
         <v>0</v>
       </c>
-      <c r="G3">
-        <f t="shared" ref="G3:G8" si="0">D3/5</f>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -742,6 +765,7 @@
         <v>5</v>
       </c>
       <c r="D4">
+        <f>70/B11</f>
         <v>70</v>
       </c>
       <c r="E4">
@@ -750,12 +774,8 @@
       <c r="F4">
         <v>1</v>
       </c>
-      <c r="G4">
-        <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -766,6 +786,7 @@
         <v>4</v>
       </c>
       <c r="D5">
+        <f>40/B11</f>
         <v>40</v>
       </c>
       <c r="E5">
@@ -774,12 +795,8 @@
       <c r="F5">
         <v>1</v>
       </c>
-      <c r="G5">
-        <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -790,6 +807,7 @@
         <v>1</v>
       </c>
       <c r="D6">
+        <f>110/B11</f>
         <v>110</v>
       </c>
       <c r="E6">
@@ -798,12 +816,8 @@
       <c r="F6">
         <v>0</v>
       </c>
-      <c r="G6">
-        <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -814,6 +828,7 @@
         <v>3</v>
       </c>
       <c r="D7">
+        <f>35/B11</f>
         <v>35</v>
       </c>
       <c r="E7">
@@ -822,12 +837,8 @@
       <c r="F7">
         <v>1</v>
       </c>
-      <c r="G7">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -838,6 +849,7 @@
         <v>3</v>
       </c>
       <c r="D8">
+        <f>45/B11</f>
         <v>45</v>
       </c>
       <c r="E8">
@@ -846,9 +858,17 @@
       <c r="F8">
         <v>1</v>
       </c>
-      <c r="G8">
-        <f t="shared" si="0"/>
-        <v>9</v>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" s="3">
+        <f>[1]Parameters!$B$20</f>
+        <v>1</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/inputData/inputDataMini.xlsx
+++ b/inputData/inputDataMini.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sillewiberg/Desktop/Skole/Speciale/Master-Thesis-eVTOL-1/inputData/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kapta\Documents\DTU\Speciale\GitHubFiles\inputData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9FAAB28-105B-574D-B4E1-4D70D006A8C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CBC61D2-0027-4913-9154-D1D94D53F935}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11940" yWindow="500" windowWidth="16860" windowHeight="16340" activeTab="2" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>
   <sheets>
     <sheet name="PlaneData" sheetId="8" r:id="rId1"/>
@@ -528,12 +528,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64A48C4B-C23A-0343-9CD4-B20C0FE9227B}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="12.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>20</v>
       </c>
@@ -541,7 +541,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>1</v>
       </c>
@@ -549,7 +549,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>2</v>
       </c>
@@ -557,7 +557,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>3</v>
       </c>
@@ -573,13 +573,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30A04F2A-161E-4502-9547-1DD0A31CBA64}">
   <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="3" max="3" width="12.5" customWidth="1"/>
     <col min="4" max="4" width="20.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -593,7 +593,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -610,7 +610,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -627,7 +627,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -644,7 +644,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>1</v>
       </c>
@@ -661,7 +661,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>1</v>
       </c>
@@ -686,13 +686,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E3CF6DF-5DC6-4F82-AD2C-07BC625FD2D9}">
-  <dimension ref="A1:F11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="5" max="5" width="19.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>14</v>
       </c>
@@ -712,7 +712,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>1</v>
       </c>
@@ -723,7 +723,7 @@
         <v>3</v>
       </c>
       <c r="D2">
-        <f>25/B11</f>
+        <f>25/B10</f>
         <v>25</v>
       </c>
       <c r="E2">
@@ -733,7 +733,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>2</v>
       </c>
@@ -744,7 +744,7 @@
         <v>1</v>
       </c>
       <c r="D3">
-        <f>50/B11</f>
+        <f>50/B10</f>
         <v>50</v>
       </c>
       <c r="E3">
@@ -754,7 +754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>3</v>
       </c>
@@ -765,7 +765,7 @@
         <v>5</v>
       </c>
       <c r="D4">
-        <f>70/B11</f>
+        <f>70/B10</f>
         <v>70</v>
       </c>
       <c r="E4">
@@ -775,7 +775,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>4</v>
       </c>
@@ -786,7 +786,7 @@
         <v>4</v>
       </c>
       <c r="D5">
-        <f>40/B11</f>
+        <f>40/B10</f>
         <v>40</v>
       </c>
       <c r="E5">
@@ -796,7 +796,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>5</v>
       </c>
@@ -807,7 +807,7 @@
         <v>1</v>
       </c>
       <c r="D6">
-        <f>110/B11</f>
+        <f>110/B10</f>
         <v>110</v>
       </c>
       <c r="E6">
@@ -817,7 +817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>6</v>
       </c>
@@ -828,7 +828,7 @@
         <v>3</v>
       </c>
       <c r="D7">
-        <f>35/B11</f>
+        <f>35/B10</f>
         <v>35</v>
       </c>
       <c r="E7">
@@ -838,7 +838,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>7</v>
       </c>
@@ -849,7 +849,7 @@
         <v>3</v>
       </c>
       <c r="D8">
-        <f>45/B11</f>
+        <f>45/B10</f>
         <v>45</v>
       </c>
       <c r="E8">
@@ -859,15 +859,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A10" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="3">
+      <c r="B10" s="3">
         <f>[1]Parameters!$B$20</f>
         <v>1</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D10" s="4" t="s">
         <v>24</v>
       </c>
     </row>

--- a/inputData/inputDataMini.xlsx
+++ b/inputData/inputDataMini.xlsx
@@ -1,22 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sillewiberg/Desktop/Skole/Speciale/Master-Thesis-eVTOL-1/inputData/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kapta\Documents\DTU\Speciale\GitHubFiles\inputData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{643F0648-698E-684C-B0F1-CDBD89F8120B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CBC61D2-0027-4913-9154-D1D94D53F935}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16340" activeTab="2" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>
   <sheets>
     <sheet name="PlaneData" sheetId="8" r:id="rId1"/>
     <sheet name="Infrastructure" sheetId="6" r:id="rId2"/>
     <sheet name="PassengerGroups" sheetId="5" r:id="rId3"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId4"/>
+  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -38,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="25">
   <si>
     <t>type</t>
   </si>
@@ -106,10 +109,13 @@
     <t>Base Vertiport</t>
   </si>
   <si>
-    <t>time_old</t>
-  </si>
-  <si>
     <t>coordinates</t>
+  </si>
+  <si>
+    <t>unit time</t>
+  </si>
+  <si>
+    <t>minuts/unit</t>
   </si>
 </sst>
 </file>
@@ -157,10 +163,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -176,6 +184,30 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Parameters"/>
+      <sheetName val="Prices"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="20">
+          <cell r="B20">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -496,12 +528,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64A48C4B-C23A-0343-9CD4-B20C0FE9227B}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="12.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>20</v>
       </c>
@@ -509,7 +541,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>1</v>
       </c>
@@ -517,7 +549,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>2</v>
       </c>
@@ -525,7 +557,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>3</v>
       </c>
@@ -541,13 +573,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30A04F2A-161E-4502-9547-1DD0A31CBA64}">
   <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="3" max="3" width="12.5" customWidth="1"/>
     <col min="4" max="4" width="20.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -558,10 +590,10 @@
         <v>3</v>
       </c>
       <c r="D1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -578,7 +610,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -595,7 +627,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -612,7 +644,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>1</v>
       </c>
@@ -629,7 +661,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>1</v>
       </c>
@@ -654,13 +686,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E3CF6DF-5DC6-4F82-AD2C-07BC625FD2D9}">
-  <dimension ref="A1:G8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="5" max="5" width="19.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>14</v>
       </c>
@@ -671,7 +703,7 @@
         <v>16</v>
       </c>
       <c r="D1" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E1" t="s">
         <v>18</v>
@@ -679,11 +711,8 @@
       <c r="F1" t="s">
         <v>19</v>
       </c>
-      <c r="G1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>1</v>
       </c>
@@ -694,6 +723,7 @@
         <v>3</v>
       </c>
       <c r="D2">
+        <f>25/B10</f>
         <v>25</v>
       </c>
       <c r="E2">
@@ -702,12 +732,8 @@
       <c r="F2">
         <v>1</v>
       </c>
-      <c r="G2">
-        <f>D2/5</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>2</v>
       </c>
@@ -718,6 +744,7 @@
         <v>1</v>
       </c>
       <c r="D3">
+        <f>50/B10</f>
         <v>50</v>
       </c>
       <c r="E3">
@@ -726,12 +753,8 @@
       <c r="F3">
         <v>0</v>
       </c>
-      <c r="G3">
-        <f t="shared" ref="G3:G8" si="0">D3/5</f>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>3</v>
       </c>
@@ -742,6 +765,7 @@
         <v>5</v>
       </c>
       <c r="D4">
+        <f>70/B10</f>
         <v>70</v>
       </c>
       <c r="E4">
@@ -750,12 +774,8 @@
       <c r="F4">
         <v>1</v>
       </c>
-      <c r="G4">
-        <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>4</v>
       </c>
@@ -766,6 +786,7 @@
         <v>4</v>
       </c>
       <c r="D5">
+        <f>40/B10</f>
         <v>40</v>
       </c>
       <c r="E5">
@@ -774,12 +795,8 @@
       <c r="F5">
         <v>1</v>
       </c>
-      <c r="G5">
-        <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>5</v>
       </c>
@@ -790,6 +807,7 @@
         <v>1</v>
       </c>
       <c r="D6">
+        <f>110/B10</f>
         <v>110</v>
       </c>
       <c r="E6">
@@ -798,12 +816,8 @@
       <c r="F6">
         <v>0</v>
       </c>
-      <c r="G6">
-        <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>6</v>
       </c>
@@ -814,6 +828,7 @@
         <v>3</v>
       </c>
       <c r="D7">
+        <f>35/B10</f>
         <v>35</v>
       </c>
       <c r="E7">
@@ -822,12 +837,8 @@
       <c r="F7">
         <v>1</v>
       </c>
-      <c r="G7">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>7</v>
       </c>
@@ -838,6 +849,7 @@
         <v>3</v>
       </c>
       <c r="D8">
+        <f>45/B10</f>
         <v>45</v>
       </c>
       <c r="E8">
@@ -846,9 +858,17 @@
       <c r="F8">
         <v>1</v>
       </c>
-      <c r="G8">
-        <f t="shared" si="0"/>
-        <v>9</v>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="3">
+        <f>[1]Parameters!$B$20</f>
+        <v>1</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/inputData/inputDataMini.xlsx
+++ b/inputData/inputDataMini.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kapta\Documents\DTU\Speciale\GitHubFiles\inputData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CBC61D2-0027-4913-9154-D1D94D53F935}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{659F7C6C-E7F9-461D-8431-B0A9BB57C364}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>
@@ -204,7 +204,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
